--- a/AAII_Financials/Quarterly/PDCO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PDCO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>PDCO</t>
   </si>
@@ -656,403 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45318</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45227</v>
+      </c>
+      <c r="F7" s="2">
         <v>45136</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45045</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44954</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44863</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44772</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44590</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44499</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44310</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44219</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44128</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44037</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43946</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43855</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43764</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43673</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43582</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43491</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43400</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43309</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43218</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43127</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43036</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42945</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42854</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42763</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1616100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1652800</v>
+      </c>
+      <c r="F8" s="3">
         <v>1576700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1721200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1600900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1626200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1523300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1638800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1596600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1649200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1614900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1561800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1551300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1553200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1245800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1286500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1456200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1418700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1328700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1436700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1396700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1404800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1336300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1400600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>1375200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>1385700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>1304100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>1445000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>1397400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>1418200</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1265100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1313700</v>
+      </c>
+      <c r="F9" s="3">
         <v>1257700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1331400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1257900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>1298100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1211100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1290500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1260000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1322700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1287900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1257400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>1226700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1232800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>992000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>992400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1144300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>1117300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1038600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>1124200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1097200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>1109700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1052700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>1110800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>1080500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>1070000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>1005100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>1109500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>1067700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>1099300</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>351000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>339100</v>
+      </c>
+      <c r="F10" s="3">
         <v>319000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>389800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>343000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>328100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>312200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>348300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>336600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>326500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>327000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>304400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>324600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>320400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>253800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>294100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>311900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>301500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>290100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>312500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>299500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>295100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>283600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>289800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>294700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>315700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>299000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>335500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>329700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>318900</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,8 +1110,10 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1173,8 +1201,14 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1296,14 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1282,38 +1322,38 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>85200</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>675100</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
+      <c r="S14" s="3">
+        <v>675100</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
@@ -1327,11 +1367,11 @@
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1351,8 +1391,14 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1440,8 +1486,14 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1522,200 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1546100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1595900</v>
+      </c>
+      <c r="F17" s="3">
         <v>1538500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1616000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1524900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1566100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1488400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1565900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1535800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1586300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1654400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1524400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1489600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1479500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1208000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1900900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1412300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1436900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1312000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1390100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1351400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1363500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1331800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1359400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>1325200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>1314000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>1247300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>1348900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>1350900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>1338400</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>56900</v>
+      </c>
+      <c r="F18" s="3">
         <v>38200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>105200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>76000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>60100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>34900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>72900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>60800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>62900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-39500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>37400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>61700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>73700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>37800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-614400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>43900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-18200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>16700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>46600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>45300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>41300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>4500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>41200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>50000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>71700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>56800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>96100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>46500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>79800</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,453 +1747,485 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F20" s="3">
         <v>11900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>4700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>3000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>18200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>1700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>14200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>19300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>6800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>89200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>4000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>4300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>3200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>2100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-11000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>2300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>31900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>1500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>5900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>1300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>1400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>2100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>1200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>1500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>1100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>1000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>85800</v>
+      </c>
+      <c r="F21" s="3">
         <v>71200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>131300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>100200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>99200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>56800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>107600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>100500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>90100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>70200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>61900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>85500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>95900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>59800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-605200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>66700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>2800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>69200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>66500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>67300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>68200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>26600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>63600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>73100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>93600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>79400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>118000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>68600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>103100</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E22" s="3">
+        <v>10600</v>
+      </c>
+      <c r="F22" s="3">
         <v>9500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>10800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>9700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>7500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>5600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>4700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>4900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>5500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>5200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>5700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>5500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>6400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>6700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>7500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>16600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>9000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>8700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>9800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>9200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>9500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>11200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>12300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>11800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>11500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>11200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>11400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>11400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>61900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>53400</v>
+      </c>
+      <c r="F23" s="3">
         <v>40600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>99100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>69300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>70800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>31100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>82400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>75200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>64100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>44500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>35700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>60500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>70500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>33200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-632900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>29500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-26900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>39900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>36400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>37600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>37700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-5500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>30300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>40400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>61500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>47100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>85800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>36100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>71300</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E24" s="3">
+        <v>13500</v>
+      </c>
+      <c r="F24" s="3">
         <v>9500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>24200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>15400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>17100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>6800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>19000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>18700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>16200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>10700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>7200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>11900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>16700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>9000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-24100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>6600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>6400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>10100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>8700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>9300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>9100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>8800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>8700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>21200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>16300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>24400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>8400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>25600</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2313,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>47600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>39900</v>
+      </c>
+      <c r="F26" s="3">
         <v>31100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>74800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>53800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>53600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>24300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>63400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>56600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>47900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>33800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>28500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>48600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>53800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>24200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-608800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>23000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-33300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>29800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>27700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>28400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>28600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>21500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>31700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>40200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>30800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>61400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>27800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>45800</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>47700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>40000</v>
+      </c>
+      <c r="F27" s="3">
         <v>31200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>75000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>53900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>54100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>24600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>63900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>57000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>48300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>34000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>28800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>48800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>54100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>24400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-608600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>23200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-33100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>30000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>28000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>28500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>28900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>21500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>31700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>40200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>30800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>61400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>27800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>45800</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2598,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2523,11 +2645,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
@@ -2538,41 +2660,47 @@
       <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>2700</v>
       </c>
-      <c r="W29" s="3" t="s">
+      <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3" t="s">
+      <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="AA29" s="3">
         <v>-600</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AB29" s="3">
         <v>77300</v>
       </c>
-      <c r="AA29" s="3" t="s">
+      <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3" t="s">
+      <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AE29" s="3">
         <v>300</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AF29" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2788,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,186 +2883,204 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-11900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-4700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-3000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-18200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-1700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-14200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-19300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-6800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-89200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-4000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-4300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-3200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>11000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-2300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-31900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-1500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-5900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>47700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>40000</v>
+      </c>
+      <c r="F33" s="3">
         <v>31200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>75000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>53900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>54100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>24600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>63900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>57000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>48300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>34000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>28800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>48800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>54100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>24400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-608600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>23200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-33100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>30000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>28000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>31200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>28900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>20900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>109000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>40200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>30800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>61700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>24500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>45800</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3168,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>47700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>40000</v>
+      </c>
+      <c r="F35" s="3">
         <v>31200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>75000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>53900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>54100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>24600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>63900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>57000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>48300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>34000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>28800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>48800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>54100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>24400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-608600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>23200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-33100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>30000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>28000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>31200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>28900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>20900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>109000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>40200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>30800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>61700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>24500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>45800</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45318</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45227</v>
+      </c>
+      <c r="F38" s="2">
         <v>45136</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45045</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44954</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44863</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44772</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44590</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44499</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44310</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44219</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44128</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44037</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43946</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43855</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43764</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43673</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43582</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43491</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43400</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43309</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43218</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43127</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43036</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42945</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42854</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42763</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3402,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,97 +3437,105 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>124000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>113900</v>
+      </c>
+      <c r="F41" s="3">
         <v>108600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>159700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>147300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>140300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>149600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>142000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>165000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>154200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>136900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>143200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>156000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>139500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>119600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>77900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>106200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>129600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>109800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>95600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>117400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>165500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>91500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>63000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>118000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>101500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>99800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>95000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>121700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>110400</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,631 +3623,679 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>484500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>490400</v>
+      </c>
+      <c r="F43" s="3">
         <v>408900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>477400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>422700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>454600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>370300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>447200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>467100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>481800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>373500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>449200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>456100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>491700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>372300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>416500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>451300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>581300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>502700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>582100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>547200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>571200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>520600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>826900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>863500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>849200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>841300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>884800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>810200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>822700</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>902700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>858000</v>
+      </c>
+      <c r="F44" s="3">
         <v>912700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>795100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>939100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>877400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>874800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>785600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>868700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>830100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>770400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>736800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>838000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>761900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>700500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>812200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>866300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>787400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>809600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>761000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>845800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>792500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>845500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>779800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>882000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>796400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>777400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>711900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>827100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>795500</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>321300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>328300</v>
+      </c>
+      <c r="F45" s="3">
         <v>342000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>351000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>335600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>353200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>311300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>304200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>289500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>333300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>330700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>286700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>273100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>263100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>267700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>236100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>268900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>189200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>160600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>165600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>169200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>176000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>184000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>103000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>116300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>96600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>97700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>111900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>112300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>104300</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1832600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1790700</v>
+      </c>
+      <c r="F46" s="3">
         <v>1772100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1783100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1844700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1825500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1706000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1679000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1790400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1799400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1611500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1615900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1723200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1656300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1460100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1542800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1692700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1687400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1582700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1604400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1679700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1705300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>1641500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>1772700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>1979800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>1843600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>1816100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>1803600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>1871200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>1832800</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>296300</v>
+      </c>
+      <c r="E47" s="3">
+        <v>283600</v>
+      </c>
+      <c r="F47" s="3">
         <v>285700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>281700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>290100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>272000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>275700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>278000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>291900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>314300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>332000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>224000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>199400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>193800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>241600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>214900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>172200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>95900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>102200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>113100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>96900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>86500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>91000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>135200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>121700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>111200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>88400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>101500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>107500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>97100</v>
       </c>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>334500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>320500</v>
+      </c>
+      <c r="F48" s="3">
         <v>320600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>305200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>288600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>282000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>290100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>283900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>286200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>287500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>294700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>296700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>304500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>379600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>377600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>382700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>390000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>391200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>391200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>305800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>290300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>289600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>289700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>290600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>287400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>286700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>294800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>298500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>300400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>303300</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>359600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>368400</v>
+      </c>
+      <c r="F49" s="3">
         <v>379200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>388300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>397800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>372800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>383400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>393200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>403600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>413600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>425400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>419600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>428200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>435700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>444200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>452200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>1140300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>1148800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>1156500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>1167400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>1174500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>1182500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>1193100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>1205400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>1216400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>1220900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>1230700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>1239000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>1247500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>1292400</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4383,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,97 +4478,109 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>117000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>126600</v>
+      </c>
+      <c r="F52" s="3">
         <v>126000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>120700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>120800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>128100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>103100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>107500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>91300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>87900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>87300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>195400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>195700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>123600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>122700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>122700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>118300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>112100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>117000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>78700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>79200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>80300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>72500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>67800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>69100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>66100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>65200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>65400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>67500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>64700</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4668,109 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2939900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2889700</v>
+      </c>
+      <c r="F54" s="3">
         <v>2883600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2879100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>2942000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>2880500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>2758400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>2741600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>2863500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>2902700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2750800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>2751500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>2851000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>2789000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>2646200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>2715400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>3513600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>3435500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>3349600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>3269300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>3320500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>3344300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>3287800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>3471700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>3674400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>3528500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>3495200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>3507900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>3594100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>3590400</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4802,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,542 +4837,580 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>683300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>688700</v>
+      </c>
+      <c r="F57" s="3">
         <v>717400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>725000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>702500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>714700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>655600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>681300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>715500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>773200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>593100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>609300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>677100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>690800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>549700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>862100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>802600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>766500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>625400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>648400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>688100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>662700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>588000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>610400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>654800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>634600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>536000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>616900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>547700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>545400</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>335100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>206000</v>
+      </c>
+      <c r="F58" s="3">
         <v>112000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>81000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>211000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>177000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>145000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>29000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>135000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>143800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>142800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>153800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>208800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>111000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>136000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>95000</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>25800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>24000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>51100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>80300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>110400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>92600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>253800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>106800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>177800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>73800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>212800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>183600</v>
       </c>
     </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>265300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>253900</v>
+      </c>
+      <c r="F59" s="3">
         <v>258300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>279300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>260300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>252100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>242900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>305300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>281600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>276100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>332000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>326700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>315100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>271100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>293100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>212800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>303800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>294900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>223000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>203300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>193400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>225900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>218800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>205400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>191500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>209300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>188300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>213300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>228000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>217700</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1283700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1148500</v>
+      </c>
+      <c r="F60" s="3">
         <v>1087700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1085300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1173700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1143800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1043600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1015700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1132100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1193100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1067900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1089700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1200900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1072900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>978800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1074900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1201500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1061400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>874200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>875700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>932700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>968900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>917300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>908400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>1100100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>950600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>902100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>903900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>988500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>946700</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>448200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>450000</v>
+      </c>
+      <c r="F61" s="3">
         <v>450600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>451200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>451900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>485500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>488800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>488600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>488400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>488100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>487800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>487500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>487900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>588300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>588000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>587800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>587500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>663500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>718100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>725300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>732600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>738300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>743700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>922000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>931400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>991200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>998500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>998300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>1001800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>1010200</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>235900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>236100</v>
+      </c>
+      <c r="F62" s="3">
         <v>234000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>224000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>214000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>209000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>199000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>194800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>198900</v>
-      </c>
-      <c r="K62" s="3">
-        <v>209600</v>
-      </c>
-      <c r="L62" s="3">
-        <v>214500</v>
       </c>
       <c r="M62" s="3">
         <v>209600</v>
       </c>
       <c r="N62" s="3">
+        <v>214500</v>
+      </c>
+      <c r="O62" s="3">
+        <v>209600</v>
+      </c>
+      <c r="P62" s="3">
         <v>227600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>235100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>224700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>216200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>252700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>251900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>253900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>187700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>182500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>181300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>179600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>179500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>179900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>219700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>210200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>211300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>217800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>227400</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5498,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5593,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5688,109 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1968500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1835400</v>
+      </c>
+      <c r="F66" s="3">
         <v>1773300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1761600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1840700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1839600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1732500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1700000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1820300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1891600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1771500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1788300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1918100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1898200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1793600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1881200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>2044100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1979600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1849300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1792000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1851400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1892300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1844600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>2009900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>2211400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>2161500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>2110700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>2113500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>2208000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>2184300</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5822,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5913,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +6008,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +6103,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6198,109 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>802900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>902800</v>
+      </c>
+      <c r="F72" s="3">
         <v>948700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>972100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>962900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>934600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>905600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>921700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>918300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>886900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>864200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>855700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>852200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>828700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>799600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>799700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>1433200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>1434800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>1492800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>1483500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>1480100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>1473400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>1469000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>1497800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>1501000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>1429700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>1450200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>1481200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>1482600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>1517800</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6388,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6483,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6578,109 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>971500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1054300</v>
+      </c>
+      <c r="F76" s="3">
         <v>1110300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1117500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1101300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1040900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1025900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1041700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1043200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1011100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>979300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>963200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>932900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>890800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>852600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>834100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1469400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1455800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1500400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1477300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1469100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1452000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>1443100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>1461800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>1463000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>1366900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>1384500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>1394400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>1386100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>1406100</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6768,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45318</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45227</v>
+      </c>
+      <c r="F80" s="2">
         <v>45136</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45045</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44954</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44863</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44772</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44590</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44499</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44310</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44219</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44128</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44037</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43946</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43855</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43764</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43673</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43582</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43491</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43400</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43309</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43218</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43127</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43036</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42945</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42854</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42763</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>47700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>40000</v>
+      </c>
+      <c r="F81" s="3">
         <v>31200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>75000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>53900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>54100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>24600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>63900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>57000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>48300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>34000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>28800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>48800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>54100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>24400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-608600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>23200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-33100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>30000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>28000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>31200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>28900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>20900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>109000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>40200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>30800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>61700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>24500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>45800</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,97 +7002,105 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>21800</v>
+      </c>
+      <c r="F83" s="3">
         <v>21000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>21400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>21200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>20900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>20200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>20600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>20400</v>
-      </c>
-      <c r="K83" s="3">
-        <v>20500</v>
-      </c>
-      <c r="L83" s="3">
-        <v>20500</v>
       </c>
       <c r="M83" s="3">
         <v>20500</v>
       </c>
       <c r="N83" s="3">
+        <v>20500</v>
+      </c>
+      <c r="O83" s="3">
+        <v>20500</v>
+      </c>
+      <c r="P83" s="3">
         <v>19500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>19000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>19900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>20300</v>
-      </c>
-      <c r="R83" s="3">
-        <v>20600</v>
-      </c>
-      <c r="S83" s="3">
-        <v>20600</v>
       </c>
       <c r="T83" s="3">
         <v>20600</v>
       </c>
       <c r="U83" s="3">
+        <v>20600</v>
+      </c>
+      <c r="V83" s="3">
+        <v>20600</v>
+      </c>
+      <c r="W83" s="3">
         <v>20300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>20500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>21100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>20900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>21000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>21000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>20700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>21100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>20800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>21000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +7188,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7283,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7378,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7473,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7568,109 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-234600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-231900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-253400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-26700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-208000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-217600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-302500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-146900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-295100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-225600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-313400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-125600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-181900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-193200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-229800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-74600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-154300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>30600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-45200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-28200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-123900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-5200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>205500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>138900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-37100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>123100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-46000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>175400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>42700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>17500</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,97 +7702,105 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="F91" s="3">
         <v>-17100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-21800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-15700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-12200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-14600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-11800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-11000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-7800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-7700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-4700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-6700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-7900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-8900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-10000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-14000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-8900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-26800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-11800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-11900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-15000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-11800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-6700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-9600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-14300</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7888,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,97 +7983,109 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>263100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>231100</v>
+      </c>
+      <c r="F94" s="3">
         <v>223800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>234300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>219400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>209500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>238400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>292600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>338800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>262600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>345000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>194800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>221000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>261500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>133400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>172700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>137000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>92700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>96800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>63200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>131200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>138800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>7600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>14300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>5500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>2800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>4700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,97 +8117,105 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="E96" s="3">
+        <v>-24900</v>
+      </c>
+      <c r="F96" s="3">
         <v>-25400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>-25400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>-25200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>-25300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>-25400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>-25400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>-25300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-25300</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-25100</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-25100</v>
       </c>
       <c r="N96" s="3">
         <v>-25100</v>
       </c>
       <c r="O96" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="P96" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-25000</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-24900</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-25000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-25000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-25500</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-24700</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-24800</v>
       </c>
       <c r="W96" s="3">
         <v>-24700</v>
       </c>
       <c r="X96" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-25300</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-24600</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-24700</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-24800</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-25200</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-25000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-23300</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-23500</v>
       </c>
     </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8303,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8398,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,271 +8493,295 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>9900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-23100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-194400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-9600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>4100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>73400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-162800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-32000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-20400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-38000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-82700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-26600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-48700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>135300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-123200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-6300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-105500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-36200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-55700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-56800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-58900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-183800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-188200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>50100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-135200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>43200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-206200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-34000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="F101" s="3">
         <v>1600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>5200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-5200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-1700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-6000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>4000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>2700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-3100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>2100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-1300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-1100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>1400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>3900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>2100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>1300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F102" s="3">
         <v>-51100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>12400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>7000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-9300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>7500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-23000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>10900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>17200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-6300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-12700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>16500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>19900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>41600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-28200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-23400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>19800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>14100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-21800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-48100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>74000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>28500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-55000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>16500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>1700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>4800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-26800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>11400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>20400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PDCO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PDCO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
   <si>
     <t>PDCO</t>
   </si>
@@ -656,429 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45500</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45409</v>
+      </c>
+      <c r="F7" s="2">
         <v>45318</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45227</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45136</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45045</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44954</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44863</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44772</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44590</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44499</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44310</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44219</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44128</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44037</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43946</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43855</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43764</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43673</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43582</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43491</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43400</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43309</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43218</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43127</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43036</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42945</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42854</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42763</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1541700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1722700</v>
+      </c>
+      <c r="F8" s="3">
         <v>1616100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1652800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1576700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1721200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1600900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1626200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1523300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1638800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1596600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1649200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1614900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1561800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1551300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1553200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1245800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1286500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1456200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1418700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1328700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1436700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1396700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1404800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>1336300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>1400600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>1375200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>1385700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>1304100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>1445000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>1397400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>1418200</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1229100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1351500</v>
+      </c>
+      <c r="F9" s="3">
         <v>1265100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1313700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1257700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>1331400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1257900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1298100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1211100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1290500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1260000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1322700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>1287900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1257400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1226700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1232800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>992000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>992400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1144300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>1117300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1038600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>1124200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1097200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>1109700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>1052700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>1110800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>1080500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>1070000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>1005100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>1109500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>1067700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>1099300</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>312600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>371200</v>
+      </c>
+      <c r="F10" s="3">
         <v>351000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>339100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>319000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>389800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>343000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>328100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>312200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>348300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>336600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>326500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>327000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>304400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>324600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>320400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>253800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>294100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>311900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>301500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>290100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>312500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>299500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>295100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>283600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>289800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>294700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>315700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>299000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>335500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>329700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>318900</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1112,8 +1137,10 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1234,14 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,8 +1335,14 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1328,38 +1367,38 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>85200</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>675100</v>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
+      <c r="U14" s="3">
+        <v>675100</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
@@ -1373,11 +1412,11 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1397,8 +1436,14 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1492,8 +1537,14 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1575,212 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1512400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1634900</v>
+      </c>
+      <c r="F17" s="3">
         <v>1546100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1595900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1538500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1616000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1524900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1566100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1488400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1565900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1535800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1586300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1654400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1524400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1489600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1479500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1208000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1900900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1412300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1436900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1312000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1390100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1351400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1363500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>1331800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>1359400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>1325200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>1314000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>1247300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>1348900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>1350900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>1338400</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>87800</v>
+      </c>
+      <c r="F18" s="3">
         <v>70000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>56900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>38200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>105200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>76000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>60100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>34900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>72900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>60800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>62900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-39500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>37400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>61700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>73700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>37800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-614400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>43900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-18200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>16700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>46600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>45300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>41300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>4500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>41200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>50000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>71700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>56800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>96100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>46500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>79800</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,483 +1814,515 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E20" s="3">
+        <v>12300</v>
+      </c>
+      <c r="F20" s="3">
         <v>3600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>7100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>11900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>4700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>3000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>18200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>1700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>14200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>19300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>6800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>89200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>4000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>4300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>3200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>2100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-11000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>2300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>31900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>1500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>5900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>1300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>1400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>2100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>1200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>1500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>1100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>1000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>53800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>123100</v>
+      </c>
+      <c r="F21" s="3">
         <v>96000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>85800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>71200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>131300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>100200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>99200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>56800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>107600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>100500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>90100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>70200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>61900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>85500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>95900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>59800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-605200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>66700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>2800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>69200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>66500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>67300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>68200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>26600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>63600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>73100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>93600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>79400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>118000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>68600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>103100</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E22" s="3">
+        <v>13000</v>
+      </c>
+      <c r="F22" s="3">
         <v>11700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>10600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>9500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>10800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>9700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>7500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>5600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>4700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>4900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>5500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>5200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>5700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>5500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>6400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>6700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>7500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>16600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>9000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>8700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>9800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>9200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>9500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>11200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>12300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>11800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>11500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>11200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>11400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>11400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>87100</v>
+      </c>
+      <c r="F23" s="3">
         <v>61900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>53400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>40600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>99100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>69300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>70800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>31100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>82400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>75200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>64100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>44500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>35700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>60500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>70500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>33200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-632900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>29500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-26900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>39900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>36400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>37600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>37700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-5500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>30300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>40400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>61500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>47100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>85800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>36100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>71300</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E24" s="3">
+        <v>20200</v>
+      </c>
+      <c r="F24" s="3">
         <v>14300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>13500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>9500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>24200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>15400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>17100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>6800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>19000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>18700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>16200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>10700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>7200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>11900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>16700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>9000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-24100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>6600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>6400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>10100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>8700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>9300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>9100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>8800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>8700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>21200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>16300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>24400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>8400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>25600</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2416,216 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>66900</v>
+      </c>
+      <c r="F26" s="3">
         <v>47600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>39900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>31100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>74800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>53800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>53600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>24300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>63400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>56600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>47900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>33800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>28500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>48600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>53800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>24200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-608800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>23000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-33300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>29800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>27700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>28400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>28600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>21500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>31700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>40200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>30800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>61400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>27800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>45800</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>67000</v>
+      </c>
+      <c r="F27" s="3">
         <v>47700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>40000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>31200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>75000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>53900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>54100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>24600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>63900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>57000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>48300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>34000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>28800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>48800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>54100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>24400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-608600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>23200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-33100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>30000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>28000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>28500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>28900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>21500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>31700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>40200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>30800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>61400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>27800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>45800</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2719,14 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2651,11 +2772,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2666,41 +2787,47 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>2700</v>
       </c>
-      <c r="Y29" s="3" t="s">
+      <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3" t="s">
+      <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AC29" s="3">
         <v>-600</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AD29" s="3">
         <v>77300</v>
       </c>
-      <c r="AC29" s="3" t="s">
+      <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3" t="s">
+      <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AG29" s="3">
         <v>300</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AH29" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2921,14 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,198 +3022,216 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="F32" s="3">
         <v>-3600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-7100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-11900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-4700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-3000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-18200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-1700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-14200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-19300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-6800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-89200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-4000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-3200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-2100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>11000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-2300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-31900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-5900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>67000</v>
+      </c>
+      <c r="F33" s="3">
         <v>47700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>40000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>31200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>75000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>53900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>54100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>24600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>63900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>57000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>48300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>34000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>28800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>48800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>54100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>24400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-608600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>23200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-33100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>30000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>28000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>31200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>28900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>20900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>109000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>40200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>30800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>61700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>24500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>45800</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3325,221 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>67000</v>
+      </c>
+      <c r="F35" s="3">
         <v>47700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>40000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>31200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>75000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>53900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>54100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>24600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>63900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>57000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>48300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>34000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>28800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>48800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>54100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>24400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-608600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>23200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-33100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>30000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>28000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>31200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>28900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>20900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>109000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>40200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>30800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>61700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>24500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>45800</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45500</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45409</v>
+      </c>
+      <c r="F38" s="2">
         <v>45318</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45227</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45136</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45045</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44954</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44863</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44772</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44590</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44499</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44310</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44219</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44128</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44037</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43946</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43855</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43764</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43673</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43582</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43491</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43400</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43309</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43218</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43127</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43036</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42945</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42854</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42763</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3573,10 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,103 +3610,111 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>148100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>114500</v>
+      </c>
+      <c r="F41" s="3">
         <v>124000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>113900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>108600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>159700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>147300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>140300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>149600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>142000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>165000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>154200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>136900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>143200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>156000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>139500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>119600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>77900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>106200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>129600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>109800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>95600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>117400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>165500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>91500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>63000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>118000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>101500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>99800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>95000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>121700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>110400</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3629,673 +3808,721 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>442300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>547300</v>
+      </c>
+      <c r="F43" s="3">
         <v>484500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>490400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>408900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>477400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>422700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>454600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>370300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>447200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>467100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>481800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>373500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>449200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>456100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>491700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>372300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>416500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>451300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>581300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>502700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>582100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>547200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>571200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>520600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>826900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>863500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>849200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>841300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>884800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>810200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>822700</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>849500</v>
+      </c>
+      <c r="E44" s="3">
+        <v>782900</v>
+      </c>
+      <c r="F44" s="3">
         <v>902700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>858000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>912700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>795100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>939100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>877400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>874800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>785600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>868700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>830100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>770400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>736800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>838000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>761900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>700500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>812200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>866300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>787400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>809600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>761000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>845800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>792500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>845500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>779800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>882000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>796400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>777400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>711900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>827100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>795500</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>322200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>334100</v>
+      </c>
+      <c r="F45" s="3">
         <v>321300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>328300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>342000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>351000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>335600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>353200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>311300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>304200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>289500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>333300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>330700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>286700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>273100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>263100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>267700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>236100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>268900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>189200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>160600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>165600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>169200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>176000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>184000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>103000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>116300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>96600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>97700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>111900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>112300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>104300</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1762100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1778800</v>
+      </c>
+      <c r="F46" s="3">
         <v>1832600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1790700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1772100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1783100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1844700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1825500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1706000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1679000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1790400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1799400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1611500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1615900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1723200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1656300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1460100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1542800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1692700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1687400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1582700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1604400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>1679700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>1705300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>1641500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>1772700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>1979800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>1843600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>1816100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>1803600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>1871200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>1832800</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>300100</v>
+      </c>
+      <c r="E47" s="3">
+        <v>296200</v>
+      </c>
+      <c r="F47" s="3">
         <v>296300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>283600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>285700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>281700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>290100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>272000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>275700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>278000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>291900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>314300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>332000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>224000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>199400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>193800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>241600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>214900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>172200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>95900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>102200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>113100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>96900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>86500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>91000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>135200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>121700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>111200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>88400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>101500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>107500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>97100</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>350600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>351400</v>
+      </c>
+      <c r="F48" s="3">
         <v>334500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>320500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>320600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>305200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>288600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>282000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>290100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>283900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>286200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>287500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>294700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>296700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>304500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>379600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>377600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>382700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>390000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>391200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>391200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>305800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>290300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>289600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>289700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>290600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>287400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>286700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>294800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>298500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>300400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>303300</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>340200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>349600</v>
+      </c>
+      <c r="F49" s="3">
         <v>359600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>368400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>379200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>388300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>397800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>372800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>383400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>393200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>403600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>413600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>425400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>419600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>428200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>435700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>444200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>452200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>1140300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>1148800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>1156500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>1167400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>1174500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>1182500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>1193100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>1205400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>1216400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>1220900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>1230700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>1239000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>1247500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>1292400</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4616,14 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,103 +4717,115 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>121800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>120800</v>
+      </c>
+      <c r="F52" s="3">
         <v>117000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>126600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>126000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>120700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>120800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>128100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>103100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>107500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>91300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>87900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>87300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>195400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>195700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>123600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>122700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>122700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>118300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>112100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>117000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>78700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>79200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>80300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>72500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>67800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>69100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>66100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>65200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>65400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>67500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>64700</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4919,115 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2874800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2896700</v>
+      </c>
+      <c r="F54" s="3">
         <v>2939900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2889700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>2883600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>2879100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>2942000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>2880500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>2758400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>2741600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2863500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>2902700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>2750800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>2751500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>2851000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>2789000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>2646200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>2715400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>3513600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>3435500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>3349600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>3269300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>3320500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>3344300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>3287800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>3471700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>3674400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>3528500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>3495200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>3507900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>3594100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>3590400</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +5061,10 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,578 +5098,616 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>657000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>745400</v>
+      </c>
+      <c r="F57" s="3">
         <v>683300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>688700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>717400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>725000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>702500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>714700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>655600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>681300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>715500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>773200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>593100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>609300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>677100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>690800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>549700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>862100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>802600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>766500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>625400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>648400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>688100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>662700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>588000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>610400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>654800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>634600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>536000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>616900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>547700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>545400</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>443900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>308800</v>
+      </c>
+      <c r="F58" s="3">
         <v>335100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>206000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>112000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>81000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>211000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>177000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>145000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>29000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>135000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>143800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>142800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>153800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>208800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>111000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>136000</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>95000</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>25800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>24000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>51100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>80300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>110400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>92600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>253800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>106800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>177800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>73800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>212800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>183600</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>256700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>278400</v>
+      </c>
+      <c r="F59" s="3">
         <v>265300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>253900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>258300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>279300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>260300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>252100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>242900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>305300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>281600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>276100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>332000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>326700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>315100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>271100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>293100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>212800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>303800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>294900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>223000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>203300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>193400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>225900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>218800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>205400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>191500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>209300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>188300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>213300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>228000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>217700</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1357500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1332600</v>
+      </c>
+      <c r="F60" s="3">
         <v>1283700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1148500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1087700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1085300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1173700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1143800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1043600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1015700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1132100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1193100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1067900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1089700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1200900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1072900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>978800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1074900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1201500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1061400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>874200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>875700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>932700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>968900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>917300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>908400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>1100100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>950600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>902100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>903900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>988500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>946700</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>327200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>328900</v>
+      </c>
+      <c r="F61" s="3">
         <v>448200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>450000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>450600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>451200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>451900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>485500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>488800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>488600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>488400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>488100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>487800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>487500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>487900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>588300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>588000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>587800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>587500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>663500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>718100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>725300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>732600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>738300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>743700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>922000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>931400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>991200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>998500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>998300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>1001800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>1010200</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>237600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>233500</v>
+      </c>
+      <c r="F62" s="3">
         <v>235900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>236100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>234000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>224000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>214000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>209000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>199000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>194800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>198900</v>
-      </c>
-      <c r="M62" s="3">
-        <v>209600</v>
-      </c>
-      <c r="N62" s="3">
-        <v>214500</v>
       </c>
       <c r="O62" s="3">
         <v>209600</v>
       </c>
       <c r="P62" s="3">
+        <v>214500</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>209600</v>
+      </c>
+      <c r="R62" s="3">
         <v>227600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>235100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>224700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>216200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>252700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>251900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>253900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>187700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>182500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>181300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>179600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>179500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>179900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>219700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>210200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>211300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>217800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>227400</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5801,14 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5902,14 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +6003,115 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1922800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1895600</v>
+      </c>
+      <c r="F66" s="3">
         <v>1968500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1835400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1773300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1761600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1840700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1839600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1732500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1700000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1820300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1891600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1771500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1788300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1918100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1898200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1793600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1881200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>2044100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1979600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1849300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1792000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1851400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1892300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1844600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>2009900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>2211400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>2161500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>2110700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>2113500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>2208000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>2184300</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +6145,10 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6242,14 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6343,14 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6444,14 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6545,115 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>772000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>831500</v>
+      </c>
+      <c r="F72" s="3">
         <v>802900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>902800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>948700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>972100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>962900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>934600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>905600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>921700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>918300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>886900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>864200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>855700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>852200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>828700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>799600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>799700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>1433200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>1434800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>1492800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>1483500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>1480100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>1473400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>1469000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>1497800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>1501000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>1429700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>1450200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>1481200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>1482600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>1517800</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6747,14 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6848,14 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6949,115 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>952000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1001100</v>
+      </c>
+      <c r="F76" s="3">
         <v>971500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1054300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1110300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1117500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1101300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1040900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1025900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1041700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1043200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1011100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>979300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>963200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>932900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>890800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>852600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>834100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1469400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1455800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1500400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1477300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>1469100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>1452000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>1443100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>1461800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>1463000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>1366900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>1384500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>1394400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>1386100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>1406100</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +7151,221 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45500</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45409</v>
+      </c>
+      <c r="F80" s="2">
         <v>45318</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45227</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45136</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45045</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44954</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44863</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44772</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44590</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44499</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44310</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44219</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44128</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44037</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43946</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43855</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43764</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43673</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43582</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43491</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43400</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43309</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43218</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43127</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43036</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42945</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42854</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42763</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>67000</v>
+      </c>
+      <c r="F81" s="3">
         <v>47700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>40000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>31200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>75000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>53900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>54100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>24600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>63900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>57000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>48300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>34000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>28800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>48800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>54100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>24400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-608600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>23200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-33100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>30000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>28000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>31200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>28900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>20900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>109000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>40200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>30800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>61700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>24500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>45800</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,103 +7399,111 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E83" s="3">
+        <v>23000</v>
+      </c>
+      <c r="F83" s="3">
         <v>22400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>21800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>21000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>21400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>21200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>20900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>20200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>20600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>20400</v>
-      </c>
-      <c r="M83" s="3">
-        <v>20500</v>
-      </c>
-      <c r="N83" s="3">
-        <v>20500</v>
       </c>
       <c r="O83" s="3">
         <v>20500</v>
       </c>
       <c r="P83" s="3">
+        <v>20500</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>20500</v>
+      </c>
+      <c r="R83" s="3">
         <v>19500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>19000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>19900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>20300</v>
-      </c>
-      <c r="T83" s="3">
-        <v>20600</v>
-      </c>
-      <c r="U83" s="3">
-        <v>20600</v>
       </c>
       <c r="V83" s="3">
         <v>20600</v>
       </c>
       <c r="W83" s="3">
+        <v>20600</v>
+      </c>
+      <c r="X83" s="3">
+        <v>20600</v>
+      </c>
+      <c r="Y83" s="3">
         <v>20300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>20500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>21100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>20900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>21000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>21000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>20700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>21100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>20800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>21000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7597,14 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7698,14 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7799,14 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7900,14 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +8001,115 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-285000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-69500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-234600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-231900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-253400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-26700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-208000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-217600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-302500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-146900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-295100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-225600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-313400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-125600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-181900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-193200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-229800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-74600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-154300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>30600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-45200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-28200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-123900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>205500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>138900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-37100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>123100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-46000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>175400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>42700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>17500</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,103 +8143,111 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-17700</v>
+        <v>-13500</v>
       </c>
       <c r="E91" s="3">
         <v>-16400</v>
       </c>
       <c r="F91" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="H91" s="3">
         <v>-17100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-21800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-15700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-12200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-14600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-11800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-11000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-7800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-7700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-4700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-7900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-6400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-8900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-10000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-14000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-8900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-26800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-11800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-11900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-15000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-11800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-9800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-6700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-9600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-14300</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8341,14 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,103 +8442,115 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>258300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>241500</v>
+      </c>
+      <c r="F94" s="3">
         <v>263100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>231100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>223800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>234300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>219400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>209500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>238400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>292600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>338800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>262600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>345000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>194800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>221000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>261500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>133400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>172700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>137000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>92700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>96800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>63200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>131200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>138800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>7600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>14300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>5500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>2800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>4700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,103 +8584,111 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E96" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="F96" s="3">
         <v>-24700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>-24900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>-25400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>-25400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>-25200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>-25300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>-25400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-25400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-25300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-25300</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-25100</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-25100</v>
       </c>
       <c r="P96" s="3">
         <v>-25100</v>
       </c>
       <c r="Q96" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="R96" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="S96" s="3">
         <v>-25000</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-24900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-25000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-25000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-25500</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-24700</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-24800</v>
       </c>
       <c r="Y96" s="3">
         <v>-24700</v>
       </c>
       <c r="Z96" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-25300</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-24600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-24700</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-24800</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-25200</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-25000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-23300</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AI96" s="3">
         <v>-23500</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8782,14 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8883,14 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,289 +8984,313 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>58800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-181800</v>
+      </c>
+      <c r="F100" s="3">
         <v>-20900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>9900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-23100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-194400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-9600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>4100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>73400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-162800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-32000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-20400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-38000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-82700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-48700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>135300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-123200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-6300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-105500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-36200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-55700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-56800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-58900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-183800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-188200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>50100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-135200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>43200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-206200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-34000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>300</v>
+      </c>
+      <c r="F101" s="3">
         <v>2500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-3800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>1600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>5200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-5200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-1700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-6000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>4000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>2700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-3100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>2100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-1300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-1100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>1400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>3900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>2100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>1300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>33600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="F102" s="3">
         <v>10100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>5300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-51100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>12400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>7000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-9300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>7500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-23000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>10900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>17200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-6300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-12700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>16500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>19900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>41600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-28200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-23400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>19800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>14100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-21800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-48100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>74000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>28500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-55000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>16500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>1700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>4800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-26800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>11400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>20400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PDCO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PDCO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
   <si>
     <t>PDCO</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45591</v>
+      </c>
+      <c r="E7" s="2">
         <v>45500</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45409</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45318</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45227</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45136</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45045</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44954</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44863</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44772</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44681</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44590</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44499</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44408</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44310</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44219</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44128</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44037</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43946</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43855</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43764</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43673</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43582</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43491</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43400</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43309</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43218</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43127</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43036</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42945</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42854</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42763</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1674400</v>
+      </c>
+      <c r="E8" s="3">
         <v>1541700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1722700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1616100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1652800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1576700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1721200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1600900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1626200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1523300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1638800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1596600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1649200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1614900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1561800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1551300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1553200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1245800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1286500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1456200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1418700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1328700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1436700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1396700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1404800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1336300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1400600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1375200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1385700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1304100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1445000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1397400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1418200</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1346300</v>
+      </c>
+      <c r="E9" s="3">
         <v>1229100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1351500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1265100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1313700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1257700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1331400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1257900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1298100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1211100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1290500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1260000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1322700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1287900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1257400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1226700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1232800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>992000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>992400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1144300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1117300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1038600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1124200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1097200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1109700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1052700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1110800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1080500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1070000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1005100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1109500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1067700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1099300</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>328100</v>
+      </c>
+      <c r="E10" s="3">
         <v>312600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>371200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>351000</v>
       </c>
-      <c r="G10" s="3">
-        <v>339100</v>
-      </c>
       <c r="H10" s="3">
-        <v>319000</v>
+        <v>339000</v>
       </c>
       <c r="I10" s="3">
+        <v>319100</v>
+      </c>
+      <c r="J10" s="3">
         <v>389800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>343000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>328100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>312200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>348300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>336600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>326500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>327000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>304400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>324600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>320400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>253800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>294100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>311900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>301500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>290100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>312500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>299500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>295100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>283600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>289800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>294700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>315700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>299000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>335500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>329700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>318900</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1150,8 +1164,8 @@
       <c r="E12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
+      <c r="F12" s="3">
+        <v>11700</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1162,8 +1176,8 @@
       <c r="I12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
+      <c r="J12" s="3">
+        <v>9100</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,13 +1358,16 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>-500</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1364,8 +1384,8 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
+      <c r="J14" s="3">
+        <v>-3600</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1373,23 +1393,23 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>85200</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
@@ -1397,11 +1417,11 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>675100</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
@@ -1418,8 +1438,8 @@
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1442,31 +1462,34 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>22900</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>22800</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>22400</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>21800</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>21400</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1512400</v>
+        <v>1629600</v>
       </c>
       <c r="E17" s="3">
-        <v>1634900</v>
+        <v>1508900</v>
       </c>
       <c r="F17" s="3">
-        <v>1546100</v>
+        <v>1631300</v>
       </c>
       <c r="G17" s="3">
-        <v>1595900</v>
+        <v>1543000</v>
       </c>
       <c r="H17" s="3">
-        <v>1538500</v>
+        <v>1592100</v>
       </c>
       <c r="I17" s="3">
-        <v>1616000</v>
+        <v>1535100</v>
       </c>
       <c r="J17" s="3">
+        <v>1616100</v>
+      </c>
+      <c r="K17" s="3">
         <v>1524900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1566100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1488400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1565900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1535800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1586300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1654400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1524400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1489600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1479500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1208000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1900900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1412300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1436900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1312000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1390100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1351400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1363500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1331800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1359400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1325200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1314000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1247300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1348900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1350900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1338400</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>29300</v>
+        <v>44800</v>
       </c>
       <c r="E18" s="3">
-        <v>87800</v>
+        <v>32900</v>
       </c>
       <c r="F18" s="3">
-        <v>70000</v>
+        <v>91400</v>
       </c>
       <c r="G18" s="3">
-        <v>56900</v>
+        <v>73100</v>
       </c>
       <c r="H18" s="3">
-        <v>38200</v>
+        <v>60600</v>
       </c>
       <c r="I18" s="3">
-        <v>105200</v>
+        <v>41600</v>
       </c>
       <c r="J18" s="3">
+        <v>105000</v>
+      </c>
+      <c r="K18" s="3">
         <v>76000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>60100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>34900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>72900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>60800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>62900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-39500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>37400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>61700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>73700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>37800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-614400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>43900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-18200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>16700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>46600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>45300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>41300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>41200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>50000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>71700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>56800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>96100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>46500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>79800</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,513 +1849,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1800</v>
+        <v>3900</v>
       </c>
       <c r="E20" s="3">
-        <v>12300</v>
+        <v>3500</v>
       </c>
       <c r="F20" s="3">
         <v>3600</v>
       </c>
       <c r="G20" s="3">
-        <v>7100</v>
+        <v>3100</v>
       </c>
       <c r="H20" s="3">
-        <v>11900</v>
+        <v>3700</v>
       </c>
       <c r="I20" s="3">
-        <v>4700</v>
+        <v>3400</v>
       </c>
       <c r="J20" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K20" s="3">
         <v>3000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>18200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>14200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>19300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>6800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>89200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>4000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>4300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-11000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>31900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>5900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>53800</v>
+        <v>63800</v>
       </c>
       <c r="E21" s="3">
-        <v>123100</v>
+        <v>52100</v>
       </c>
       <c r="F21" s="3">
-        <v>96000</v>
+        <v>110700</v>
       </c>
       <c r="G21" s="3">
-        <v>85800</v>
+        <v>92400</v>
       </c>
       <c r="H21" s="3">
-        <v>71200</v>
+        <v>78700</v>
       </c>
       <c r="I21" s="3">
-        <v>131300</v>
+        <v>59300</v>
       </c>
       <c r="J21" s="3">
+        <v>122900</v>
+      </c>
+      <c r="K21" s="3">
         <v>100200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>99200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>56800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>107600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>100500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>90100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>70200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>61900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>85500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>95900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>59800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-605200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>66700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>69200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>66500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>67300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>68200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>26600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>63600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>73100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>93600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>79400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>118000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>68600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>103100</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>13200</v>
+        <v>12500</v>
       </c>
       <c r="E22" s="3">
-        <v>13000</v>
+        <v>17000</v>
       </c>
       <c r="F22" s="3">
-        <v>11700</v>
+        <v>6700</v>
       </c>
       <c r="G22" s="3">
-        <v>10600</v>
+        <v>15200</v>
       </c>
       <c r="H22" s="3">
+        <v>7900</v>
+      </c>
+      <c r="I22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J22" s="3">
+        <v>10100</v>
+      </c>
+      <c r="K22" s="3">
+        <v>9700</v>
+      </c>
+      <c r="L22" s="3">
+        <v>7500</v>
+      </c>
+      <c r="M22" s="3">
+        <v>5600</v>
+      </c>
+      <c r="N22" s="3">
+        <v>4700</v>
+      </c>
+      <c r="O22" s="3">
+        <v>4900</v>
+      </c>
+      <c r="P22" s="3">
+        <v>5500</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>5200</v>
+      </c>
+      <c r="R22" s="3">
+        <v>5700</v>
+      </c>
+      <c r="S22" s="3">
+        <v>5500</v>
+      </c>
+      <c r="T22" s="3">
+        <v>6400</v>
+      </c>
+      <c r="U22" s="3">
+        <v>6700</v>
+      </c>
+      <c r="V22" s="3">
+        <v>7500</v>
+      </c>
+      <c r="W22" s="3">
+        <v>16600</v>
+      </c>
+      <c r="X22" s="3">
+        <v>9000</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>8700</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>9800</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AB22" s="3">
         <v>9500</v>
       </c>
-      <c r="I22" s="3">
-        <v>10800</v>
-      </c>
-      <c r="J22" s="3">
-        <v>9700</v>
-      </c>
-      <c r="K22" s="3">
-        <v>7500</v>
-      </c>
-      <c r="L22" s="3">
-        <v>5600</v>
-      </c>
-      <c r="M22" s="3">
-        <v>4700</v>
-      </c>
-      <c r="N22" s="3">
-        <v>4900</v>
-      </c>
-      <c r="O22" s="3">
-        <v>5500</v>
-      </c>
-      <c r="P22" s="3">
-        <v>5200</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>5700</v>
-      </c>
-      <c r="R22" s="3">
-        <v>5500</v>
-      </c>
-      <c r="S22" s="3">
-        <v>6400</v>
-      </c>
-      <c r="T22" s="3">
-        <v>6700</v>
-      </c>
-      <c r="U22" s="3">
-        <v>7500</v>
-      </c>
-      <c r="V22" s="3">
-        <v>16600</v>
-      </c>
-      <c r="W22" s="3">
-        <v>9000</v>
-      </c>
-      <c r="X22" s="3">
-        <v>8700</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>9800</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>9200</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>9500</v>
-      </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>11200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>12300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>11800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>11500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>11200</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>11400</v>
       </c>
       <c r="AH22" s="3">
         <v>11400</v>
       </c>
       <c r="AI22" s="3">
+        <v>11400</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E23" s="3">
         <v>17900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>87100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>61900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>53400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>40600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>99100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>69300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>70800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>31100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>82400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>75200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>64100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>44500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>35700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>60500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>70500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>33200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-632900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>29500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-26900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>39900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>36400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>37600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>37700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-5500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>30300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>40400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>61500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>47100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>85800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>36100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>71300</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E24" s="3">
         <v>4200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>20200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>14300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>13500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>9500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>24200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>15400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>17100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>19000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>18700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>16200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>10700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>11900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>16700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>9000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-24100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>6400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>10100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>8700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>9300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>9100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>8800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>8700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>21200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>16300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>24400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>8400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>25600</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E26" s="3">
         <v>13600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>66900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>47600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>39900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>31100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>74800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>53800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>53600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>24300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>63400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>56600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>47900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>33800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>28500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>48600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>53800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>24200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-608800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>23000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-33300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>29800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>27700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>28400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>28600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>21500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>31700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>40200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>30800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>61400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>27800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>45800</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E27" s="3">
         <v>13700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>67000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>47700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>40000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>31200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>75000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>53900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>54100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>24600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>63900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>57000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>48300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>34000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>28800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>48800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>54100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>24400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-608600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>23200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-33100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>30000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>28000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>28500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>28900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>21500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>31700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>40200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>30800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>61400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>27800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>45800</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2778,8 +2839,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2793,41 +2854,44 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>2700</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-600</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>77300</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>300</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-3200</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1800</v>
+        <v>-3900</v>
       </c>
       <c r="E32" s="3">
-        <v>-12300</v>
+        <v>-3500</v>
       </c>
       <c r="F32" s="3">
         <v>-3600</v>
       </c>
       <c r="G32" s="3">
-        <v>-7100</v>
+        <v>-3100</v>
       </c>
       <c r="H32" s="3">
-        <v>-11900</v>
+        <v>-3700</v>
       </c>
       <c r="I32" s="3">
-        <v>-4700</v>
+        <v>-3400</v>
       </c>
       <c r="J32" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-3000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-18200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-14200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-19300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-6800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-89200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-4000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-4300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>11000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-31900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-5900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E33" s="3">
         <v>13700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>67000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>47700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>40000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>31200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>75000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>53900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>54100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>24600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>63900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>57000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>48300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>34000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>28800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>48800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>54100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>24400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-608600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>23200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-33100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>30000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>28000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>31200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>28900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>20900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>109000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>40200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>30800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>61700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>24500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>45800</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E35" s="3">
         <v>13700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>67000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>47700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>40000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>31200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>75000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>53900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>54100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>24600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>63900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>57000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>48300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>34000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>28800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>48800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>54100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>24400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-608600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>23200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-33100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>30000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>28000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>31200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>28900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>20900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>109000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>40200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>30800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>61700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>24500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>45800</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45591</v>
+      </c>
+      <c r="E38" s="2">
         <v>45500</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45409</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45318</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45227</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45136</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45045</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44954</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44863</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44772</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44681</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44590</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44499</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44408</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44310</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44219</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44128</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44037</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43946</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43855</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43764</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43673</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43582</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43491</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43400</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43309</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43218</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43127</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43036</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42945</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42854</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42763</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,132 +3698,136 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>157900</v>
+      </c>
+      <c r="E41" s="3">
         <v>148100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>114500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>124000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>113900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>108600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>159700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>147300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>140300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>149600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>142000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>165000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>154200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>136900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>143200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>156000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>139500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>119600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>77900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>106200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>129600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>109800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>95600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>117400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>165500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>91500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>63000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>118000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>101500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>99800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>95000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>121700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>110400</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>6800</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3814,715 +3904,739 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>442300</v>
+        <v>713300</v>
       </c>
       <c r="E43" s="3">
-        <v>547300</v>
+        <v>614300</v>
       </c>
       <c r="F43" s="3">
-        <v>484500</v>
+        <v>746100</v>
       </c>
       <c r="G43" s="3">
-        <v>490400</v>
+        <v>712500</v>
       </c>
       <c r="H43" s="3">
-        <v>408900</v>
+        <v>692400</v>
       </c>
       <c r="I43" s="3">
-        <v>477400</v>
+        <v>619200</v>
       </c>
       <c r="J43" s="3">
+        <v>705300</v>
+      </c>
+      <c r="K43" s="3">
         <v>422700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>454600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>370300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>447200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>467100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>481800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>373500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>449200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>456100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>491700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>372300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>416500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>451300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>581300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>502700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>582100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>547200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>571200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>520600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>826900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>863500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>849200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>841300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>884800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>810200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>822700</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>823700</v>
+      </c>
+      <c r="E44" s="3">
         <v>849500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>782900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>902700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>858000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>912700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>795100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>939100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>877400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>874800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>785600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>868700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>830100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>770400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>736800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>838000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>761900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>700500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>812200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>866300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>787400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>809600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>761000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>845800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>792500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>845500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>779800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>882000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>796400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>777400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>711900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>827100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>795500</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>322200</v>
-      </c>
-      <c r="E45" s="3">
-        <v>334100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>321300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>328300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>342000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>351000</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>335600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>353200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>311300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>304200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>289500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>333300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>330700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>286700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>273100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>263100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>267700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>236100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>268900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>189200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>160600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>165600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>169200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>176000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>184000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>103000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>116300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>96600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>97700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>111900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>112300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>104300</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1842000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1762100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1778800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1832600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1790700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1772100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1783100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1844700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1825500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1706000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1679000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1790400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1799400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1611500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1615900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1723200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1656300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1460100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1542800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1692700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1687400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1582700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1604400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1679700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1705300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1641500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1772700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1979800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1843600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1816100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1803600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1871200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1832800</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>300100</v>
+        <v>91900</v>
       </c>
       <c r="E47" s="3">
-        <v>296200</v>
+        <v>184200</v>
       </c>
       <c r="F47" s="3">
-        <v>296300</v>
+        <v>187500</v>
       </c>
       <c r="G47" s="3">
-        <v>283600</v>
+        <v>180800</v>
       </c>
       <c r="H47" s="3">
-        <v>285700</v>
+        <v>190500</v>
       </c>
       <c r="I47" s="3">
-        <v>281700</v>
+        <v>188500</v>
       </c>
       <c r="J47" s="3">
+        <v>183200</v>
+      </c>
+      <c r="K47" s="3">
         <v>290100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>272000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>275700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>278000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>291900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>314300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>332000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>224000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>199400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>193800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>241600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>214900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>172200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>95900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>102200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>113100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>96900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>86500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>91000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>135200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>121700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>111200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>88400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>101500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>107500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>97100</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>350200</v>
+      </c>
+      <c r="E48" s="3">
         <v>350600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>351400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>334500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>320500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>320600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>305200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>288600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>282000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>290100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>283900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>286200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>287500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>294700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>296700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>304500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>379600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>377600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>382700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>390000</v>
-      </c>
-      <c r="W48" s="3">
-        <v>391200</v>
       </c>
       <c r="X48" s="3">
         <v>391200</v>
       </c>
       <c r="Y48" s="3">
+        <v>391200</v>
+      </c>
+      <c r="Z48" s="3">
         <v>305800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>290300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>289600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>289700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>290600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>287400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>286700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>294800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>298500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>300400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>303300</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>341200</v>
+      </c>
+      <c r="E49" s="3">
         <v>340200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>349600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>359600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>368400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>379200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>388300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>397800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>372800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>383400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>393200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>403600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>413600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>425400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>419600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>428200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>435700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>444200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>452200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1140300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1148800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1156500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1167400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1174500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1182500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1193100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1205400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1216400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1220900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1230700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1239000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1247500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1292400</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>121800</v>
+        <v>220200</v>
       </c>
       <c r="E52" s="3">
+        <v>237700</v>
+      </c>
+      <c r="F52" s="3">
+        <v>229500</v>
+      </c>
+      <c r="G52" s="3">
+        <v>232500</v>
+      </c>
+      <c r="H52" s="3">
+        <v>219600</v>
+      </c>
+      <c r="I52" s="3">
+        <v>223300</v>
+      </c>
+      <c r="J52" s="3">
+        <v>219200</v>
+      </c>
+      <c r="K52" s="3">
         <v>120800</v>
       </c>
-      <c r="F52" s="3">
-        <v>117000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>126600</v>
-      </c>
-      <c r="H52" s="3">
-        <v>126000</v>
-      </c>
-      <c r="I52" s="3">
-        <v>120700</v>
-      </c>
-      <c r="J52" s="3">
-        <v>120800</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>128100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>103100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>107500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>91300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>87900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>87300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>195400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>195700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>123600</v>
-      </c>
-      <c r="T52" s="3">
-        <v>122700</v>
       </c>
       <c r="U52" s="3">
         <v>122700</v>
       </c>
       <c r="V52" s="3">
+        <v>122700</v>
+      </c>
+      <c r="W52" s="3">
         <v>118300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>112100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>117000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>78700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>79200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>80300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>72500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>67800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>69100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>66100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>65200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>65400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>67500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>64700</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2845600</v>
+      </c>
+      <c r="E54" s="3">
         <v>2874800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2896700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2939900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2889700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2883600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2879100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2942000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2880500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2758400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2741600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2863500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2902700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2750800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2751500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2851000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2789000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2646200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2715400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3513600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3435500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3349600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3269300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3320500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3344300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3287800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3471700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3674400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3528500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3495200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3507900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3594100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>3590400</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,614 +5230,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>731300</v>
+      </c>
+      <c r="E57" s="3">
         <v>657000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>745400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>683300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>688700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>717400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>725000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>702500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>714700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>655600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>681300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>715500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>773200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>593100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>609300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>677100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>690800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>549700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>862100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>802600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>766500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>625400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>648400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>688100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>662700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>588000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>610400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>654800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>634600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>536000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>616900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>547700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>545400</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>443900</v>
+        <v>393700</v>
       </c>
       <c r="E58" s="3">
-        <v>308800</v>
+        <v>478100</v>
       </c>
       <c r="F58" s="3">
-        <v>335100</v>
+        <v>341800</v>
       </c>
       <c r="G58" s="3">
-        <v>206000</v>
+        <v>366600</v>
       </c>
       <c r="H58" s="3">
-        <v>112000</v>
+        <v>236400</v>
       </c>
       <c r="I58" s="3">
-        <v>81000</v>
+        <v>142100</v>
       </c>
       <c r="J58" s="3">
+        <v>109700</v>
+      </c>
+      <c r="K58" s="3">
         <v>211000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>177000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>145000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>29000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>135000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>143800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>142800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>153800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>208800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>111000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>136000</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>95000</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
       <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
         <v>25800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>24000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>51100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>80300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>110400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>92600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>253800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>106800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>177800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>73800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>212800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>183600</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>256700</v>
+        <v>36300</v>
       </c>
       <c r="E59" s="3">
-        <v>278400</v>
+        <v>35500</v>
       </c>
       <c r="F59" s="3">
-        <v>265300</v>
+        <v>37400</v>
       </c>
       <c r="G59" s="3">
-        <v>253900</v>
+        <v>40300</v>
       </c>
       <c r="H59" s="3">
-        <v>258300</v>
+        <v>40100</v>
       </c>
       <c r="I59" s="3">
-        <v>279300</v>
+        <v>37500</v>
       </c>
       <c r="J59" s="3">
+        <v>36900</v>
+      </c>
+      <c r="K59" s="3">
         <v>260300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>252100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>242900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>305300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>281600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>276100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>332000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>326700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>315100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>271100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>293100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>212800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>303800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>294900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>223000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>203300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>193400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>225900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>218800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>205400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>191500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>209300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>188300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>213300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>228000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>217700</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1344400</v>
+      </c>
+      <c r="E60" s="3">
         <v>1357500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1332600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1283700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1148500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1087700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1085300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1173700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1143800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1043600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1015700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1132100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1193100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1067900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1089700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1200900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1072900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>978800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1074900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1201500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1061400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>874200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>875700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>932700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>968900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>917300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>908400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1100100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>950600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>902100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>903900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>988500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>946700</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>327200</v>
+        <v>424500</v>
       </c>
       <c r="E61" s="3">
-        <v>328900</v>
+        <v>434800</v>
       </c>
       <c r="F61" s="3">
-        <v>448200</v>
+        <v>434600</v>
       </c>
       <c r="G61" s="3">
-        <v>450000</v>
+        <v>538900</v>
       </c>
       <c r="H61" s="3">
-        <v>450600</v>
+        <v>541200</v>
       </c>
       <c r="I61" s="3">
-        <v>451200</v>
+        <v>538400</v>
       </c>
       <c r="J61" s="3">
+        <v>531600</v>
+      </c>
+      <c r="K61" s="3">
         <v>451900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>485500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>488800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>488600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>488400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>488100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>487800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>487500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>487900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>588300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>588000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>587800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>587500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>663500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>718100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>725300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>732600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>738300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>743700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>922000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>931400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>991200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>998500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>998300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1001800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1010200</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>237600</v>
+        <v>113200</v>
       </c>
       <c r="E62" s="3">
-        <v>233500</v>
+        <v>130000</v>
       </c>
       <c r="F62" s="3">
-        <v>235900</v>
+        <v>23400</v>
       </c>
       <c r="G62" s="3">
-        <v>236100</v>
+        <v>145100</v>
       </c>
       <c r="H62" s="3">
-        <v>234000</v>
+        <v>144900</v>
       </c>
       <c r="I62" s="3">
-        <v>224000</v>
+        <v>146200</v>
       </c>
       <c r="J62" s="3">
+        <v>24500</v>
+      </c>
+      <c r="K62" s="3">
         <v>214000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>209000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>199000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>194800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>198900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>209600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>214500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>209600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>227600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>235100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>224700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>216200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>252700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>251900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>253900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>187700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>182500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>181300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>179600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>179500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>179900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>219700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>210200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>211300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>217800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>227400</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1922800</v>
+        <v>1882200</v>
       </c>
       <c r="E66" s="3">
-        <v>1895600</v>
+        <v>1922300</v>
       </c>
       <c r="F66" s="3">
-        <v>1968500</v>
+        <v>1895000</v>
       </c>
       <c r="G66" s="3">
-        <v>1835400</v>
+        <v>1967800</v>
       </c>
       <c r="H66" s="3">
-        <v>1773300</v>
+        <v>1834600</v>
       </c>
       <c r="I66" s="3">
-        <v>1761600</v>
+        <v>1772400</v>
       </c>
       <c r="J66" s="3">
+        <v>1760600</v>
+      </c>
+      <c r="K66" s="3">
         <v>1840700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1839600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1732500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1700000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1820300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1891600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1771500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1788300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1918100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1898200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1793600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1881200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2044100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1979600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1849300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1792000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1851400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1892300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1844600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2009900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2211400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2161500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2110700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2113500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2208000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2184300</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>775500</v>
+      </c>
+      <c r="E72" s="3">
         <v>772000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>831500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>802900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>902800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>948700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>972100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>962900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>934600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>905600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>921700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>918300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>886900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>864200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>855700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>852200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>828700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>799600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>799700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1433200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1434800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1492800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1483500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1480100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1473400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1469000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1497800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1501000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1429700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1450200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1481200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1482600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1517800</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>963000</v>
+      </c>
+      <c r="E76" s="3">
         <v>952000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1001100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>971500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1054300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1110300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1117500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1101300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1040900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1025900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1041700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1043200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1011100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>979300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>963200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>932900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>890800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>852600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>834100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1469400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1455800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1500400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1477300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1469100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1452000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1443100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1461800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1463000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1366900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1384500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1394400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1386100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1406100</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45591</v>
+      </c>
+      <c r="E80" s="2">
         <v>45500</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45409</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45318</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45227</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45136</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45045</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44954</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44863</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44772</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44681</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44590</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44499</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44408</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44310</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44219</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44128</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44037</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43946</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43855</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43764</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43673</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43582</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43491</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43400</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43309</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43218</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43127</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43036</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42945</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42854</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42763</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E81" s="3">
         <v>13700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>67000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>47700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>40000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>31200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>75000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>53900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>54100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>24600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>63900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>57000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>48300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>34000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>28800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>48800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>54100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>24400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-608600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>23200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-33100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>30000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>28000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>31200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>28900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>20900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>109000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>40200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>30800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>61700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>24500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>45800</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,46 +7599,47 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>22800</v>
+        <v>12200</v>
       </c>
       <c r="E83" s="3">
-        <v>23000</v>
+        <v>11400</v>
       </c>
       <c r="F83" s="3">
-        <v>22400</v>
+        <v>11600</v>
       </c>
       <c r="G83" s="3">
-        <v>21800</v>
+        <v>11700</v>
       </c>
       <c r="H83" s="3">
-        <v>21000</v>
+        <v>11600</v>
       </c>
       <c r="I83" s="3">
-        <v>21400</v>
+        <v>10800</v>
       </c>
       <c r="J83" s="3">
+        <v>11200</v>
+      </c>
+      <c r="K83" s="3">
         <v>21200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>20900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>20200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>20600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>20400</v>
-      </c>
-      <c r="O83" s="3">
-        <v>20500</v>
       </c>
       <c r="P83" s="3">
         <v>20500</v>
@@ -7449,19 +7648,19 @@
         <v>20500</v>
       </c>
       <c r="R83" s="3">
+        <v>20500</v>
+      </c>
+      <c r="S83" s="3">
         <v>19500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>19000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>19900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>20300</v>
-      </c>
-      <c r="V83" s="3">
-        <v>20600</v>
       </c>
       <c r="W83" s="3">
         <v>20600</v>
@@ -7470,40 +7669,43 @@
         <v>20600</v>
       </c>
       <c r="Y83" s="3">
+        <v>20600</v>
+      </c>
+      <c r="Z83" s="3">
         <v>20300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>20500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>21100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>20900</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>21000</v>
       </c>
       <c r="AD83" s="3">
         <v>21000</v>
       </c>
       <c r="AE83" s="3">
+        <v>21000</v>
+      </c>
+      <c r="AF83" s="3">
         <v>20700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>21100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>20800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>21000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-173700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-285000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-69500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-234600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-231900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-253400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-26700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-208000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-217600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-302500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-146900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-295100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-225600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-313400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-125600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-181900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-193200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-229800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-74600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-154300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>30600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-45200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-28200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-123900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>205500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>138900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-37100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>123100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-46000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>175400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>42700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>17500</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-16400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-17700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-16400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-17100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-21800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-15700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-12200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-14600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-6400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-8900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-10000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-14000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-8900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-26800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-11800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-11900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-10200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-15000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-9800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-6700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-9600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-14300</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>291000</v>
+      </c>
+      <c r="E94" s="3">
         <v>258300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>241500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>263100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>231100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>223800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>234300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>219400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>209500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>238400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>292600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>338800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>262600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>345000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>194800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>221000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>261500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>133400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>172700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>137000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>92700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>96800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>63200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>131200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>138800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>7600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>14300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>5500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>2800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>4700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,49 +8819,50 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-23300</v>
+        <v>22900</v>
       </c>
       <c r="E96" s="3">
-        <v>-23300</v>
+        <v>23300</v>
       </c>
       <c r="F96" s="3">
-        <v>-24700</v>
+        <v>23300</v>
       </c>
       <c r="G96" s="3">
-        <v>-24900</v>
+        <v>24700</v>
       </c>
       <c r="H96" s="3">
-        <v>-25400</v>
+        <v>24900</v>
       </c>
       <c r="I96" s="3">
-        <v>-25400</v>
+        <v>25400</v>
       </c>
       <c r="J96" s="3">
+        <v>25400</v>
+      </c>
+      <c r="K96" s="3">
         <v>-25200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-25300</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-25400</v>
       </c>
       <c r="M96" s="3">
         <v>-25400</v>
       </c>
       <c r="N96" s="3">
-        <v>-25300</v>
+        <v>-25400</v>
       </c>
       <c r="O96" s="3">
         <v>-25300</v>
       </c>
       <c r="P96" s="3">
-        <v>-25100</v>
+        <v>-25300</v>
       </c>
       <c r="Q96" s="3">
         <v>-25100</v>
@@ -8637,58 +8871,61 @@
         <v>-25100</v>
       </c>
       <c r="S96" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="T96" s="3">
         <v>-25000</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-24900</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-25000</v>
       </c>
       <c r="W96" s="3">
         <v>-25000</v>
       </c>
       <c r="X96" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-25500</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-24700</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-24800</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-24700</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-25300</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-24600</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-24700</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-24800</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-25200</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-25000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-23300</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-23500</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-107700</v>
+      </c>
+      <c r="E100" s="3">
         <v>58800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-181800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-20900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>9900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-23100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-194400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-9600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>73400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-162800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-32000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-20400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-38000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-82700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-26600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-48700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>135300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-123200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-6300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-105500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-36200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-55700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-56800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-58900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-183800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-188200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>50100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-135200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>43200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-206200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-34000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>1500</v>
+        <v>-3800</v>
       </c>
       <c r="E101" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="G101" s="3">
+        <v>5200</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="K101" s="3">
+        <v>5200</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="O101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="P101" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>200</v>
+      </c>
+      <c r="R101" s="3">
+        <v>900</v>
+      </c>
+      <c r="S101" s="3">
+        <v>4000</v>
+      </c>
+      <c r="T101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
-        <v>2500</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="H101" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-800</v>
-      </c>
-      <c r="J101" s="3">
-        <v>5200</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-800</v>
-      </c>
-      <c r="O101" s="3">
-        <v>600</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="U101" s="3">
+        <v>2700</v>
+      </c>
+      <c r="V101" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="W101" s="3">
         <v>200</v>
       </c>
-      <c r="Q101" s="3">
-        <v>900</v>
-      </c>
-      <c r="R101" s="3">
-        <v>4000</v>
-      </c>
-      <c r="S101" s="3">
-        <v>300</v>
-      </c>
-      <c r="T101" s="3">
-        <v>2700</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="V101" s="3">
-        <v>200</v>
-      </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>3900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>2100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E102" s="3">
         <v>33600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-9500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-51100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>12400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>7000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-9300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>7500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-23000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>10900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>17200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-12700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>16500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>19900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>41600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-28200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-23400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>19800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>14100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-21800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-48100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>74000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>28500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-55000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>16500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>4800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-26800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>11400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>20400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PDCO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PDCO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>PDCO</t>
   </si>
@@ -656,467 +656,480 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45682</v>
+      </c>
+      <c r="E7" s="2">
         <v>45591</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45500</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45409</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45318</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45227</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45136</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45045</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44954</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44863</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44772</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44590</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44499</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44408</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44310</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44219</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44128</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44037</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43946</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43855</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43764</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43673</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43582</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43491</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43400</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43309</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43218</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43127</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43036</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42945</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42854</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42763</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1572400</v>
+      </c>
+      <c r="E8" s="3">
         <v>1674400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1541700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1722700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1616100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1652800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1576700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1721200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1600900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1626200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1523300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1638800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1596600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1649200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1614900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1561800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1551300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1553200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1245800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1286500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1456200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1418700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1328700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1436700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1396700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1404800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1336300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1400600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1375200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1385700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1304100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1445000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1397400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1418200</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1251600</v>
+      </c>
+      <c r="E9" s="3">
         <v>1346300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1229100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1351500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1265100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1313700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1257700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1331400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1257900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1298100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1211100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1290500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1260000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1322700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1287900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1257400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1226700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1232800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>992000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>992400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1144300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1117300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1038600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1124200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1097200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1109700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1052700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1110800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1080500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1070000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1005100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1109500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1067700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1099300</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>320800</v>
+      </c>
+      <c r="E10" s="3">
         <v>328100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>312600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>371200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>351000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>339000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>319100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>389800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>343000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>328100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>312200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>348300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>336600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>326500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>327000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>304400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>324600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>320400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>253800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>294100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>311900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>301500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>290100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>312500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>299500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>295100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>283600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>289800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>294700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>315700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>299000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>335500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>329700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>318900</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1166,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1164,11 +1178,11 @@
       <c r="E12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="3">
         <v>11700</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
@@ -1176,11 +1190,11 @@
       <c r="I12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="3">
         <v>9100</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
@@ -1257,8 +1271,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,16 +1378,19 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>-500</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -1384,11 +1404,11 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>-3600</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
@@ -1396,23 +1416,23 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>85200</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
@@ -1420,11 +1440,11 @@
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3">
         <v>675100</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
@@ -1441,8 +1461,8 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1465,35 +1485,38 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E15" s="3">
         <v>22900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>22800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>23000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>22400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>21800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>21000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>21400</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1569,8 +1592,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1630,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1524300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1629600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1508900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1631300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1543000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1592100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1535100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1616100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1524900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1566100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1488400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1565900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1535800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1586300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1654400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1524400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1489600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1479500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1208000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1900900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1412300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1436900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1312000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1390100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1351400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1363500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1331800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1359400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1325200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1314000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1247300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1348900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1350900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1338400</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>48100</v>
+      </c>
+      <c r="E18" s="3">
         <v>44800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>32900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>91400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>73100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>60600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>41600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>105000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>76000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>60100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>34900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>72900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>60800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>62900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-39500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>37400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>61700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>73700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>37800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-614400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>43900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-18200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>16700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>46600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>45300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>41300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>41200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>50000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>71700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>56800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>96100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>46500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>79800</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,528 +1883,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E20" s="3">
         <v>3900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>18200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>14200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>19300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>89200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>4000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>4300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-11000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>31900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>5900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>68600</v>
+      </c>
+      <c r="E21" s="3">
         <v>63800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>52100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>110700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>92400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>78700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>59300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>122900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>100200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>99200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>56800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>107600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>100500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>90100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>70200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>61900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>85500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>95900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>59800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-605200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>66700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>69200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>66500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>67300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>68200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>26600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>63600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>73100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>93600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>79400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>118000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>68600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>103100</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E22" s="3">
         <v>12500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>17000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>6700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>15200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>7900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>10100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>9700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>5600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>4700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>4900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>5500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>5200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>5700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>5500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>6400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>6700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>7500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>16600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>9000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>8700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>9800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>9200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>9500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>11200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>12300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>11800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>11500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>11200</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>11400</v>
       </c>
       <c r="AI22" s="3">
         <v>11400</v>
       </c>
       <c r="AJ22" s="3">
+        <v>11400</v>
+      </c>
+      <c r="AK22" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>42800</v>
+      </c>
+      <c r="E23" s="3">
         <v>35500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>17900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>87100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>61900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>53400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>40600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>99100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>69300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>70800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>31100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>82400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>75200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>64100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>44500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>35700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>60500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>70500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>33200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-632900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>29500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-26900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>39900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>36400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>37600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>37700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-5500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>30300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>40400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>61500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>47100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>85800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>36100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>71300</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E24" s="3">
         <v>8800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>20200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>14300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>13500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>9500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>24200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>15400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>17100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>19000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>18700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>16200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>10700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>11900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>16700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>9000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-24100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>6600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>6400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>10100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>8700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>9300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>9100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>8800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>8700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>21200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>16300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>24400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>8400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>25600</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2523,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E26" s="3">
         <v>26700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>13600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>66900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>47600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>39900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>31100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>74800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>53800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>53600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>24300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>63400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>56600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>47900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>33800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>28500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>48600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>53800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>24200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-608800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>23000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-33300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>29800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>27700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>28400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>28600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>21500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>31700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>40200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>30800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>61400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>27800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>45800</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>31300</v>
+      </c>
+      <c r="E27" s="3">
         <v>26800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>13700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>67000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>47700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>40000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>31200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>75000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>53900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>54100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>24600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>63900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>57000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>48300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>34000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>28800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>48800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>54100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>24400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-608600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>23200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-33100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>30000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>28000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>28500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>28900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>21500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>31700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>40200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>30800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>61400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>27800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>45800</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2844,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2842,8 +2903,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2857,41 +2918,44 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>2700</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-600</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>77300</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI29" s="3">
         <v>300</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-3200</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3058,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,216 +3165,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-18200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-14200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-19300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-89200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-4000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-4300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>11000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-31900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-5900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>31300</v>
+      </c>
+      <c r="E33" s="3">
         <v>26800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>13700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>67000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>47700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>40000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>31200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>75000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>53900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>54100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>24600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>63900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>57000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>48300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>34000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>28800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>48800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>54100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>24400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-608600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>23200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-33100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>30000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>28000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>31200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>28900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>20900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>109000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>40200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>30800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>61700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>24500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>45800</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3486,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>31300</v>
+      </c>
+      <c r="E35" s="3">
         <v>26800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>13700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>67000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>47700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>40000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>31200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>75000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>53900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>54100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>24600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>63900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>57000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>48300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>34000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>28800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>48800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>54100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>24400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-608600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>23200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-33100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>30000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>28000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>31200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>28900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>20900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>109000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>40200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>30800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>61700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>24500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>45800</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45682</v>
+      </c>
+      <c r="E38" s="2">
         <v>45591</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45500</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45409</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45318</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45227</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45136</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45045</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44954</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44863</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44772</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44590</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44499</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44408</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44310</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44219</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44128</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44037</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43946</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43855</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43764</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43673</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43582</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43491</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43400</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43309</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43218</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43127</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43036</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42945</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42854</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42763</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3746,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,139 +3785,143 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>135000</v>
+      </c>
+      <c r="E41" s="3">
         <v>157900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>148100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>114500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>124000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>113900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>108600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>159700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>147300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>140300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>149600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>142000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>165000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>154200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>136900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>143200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>156000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>139500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>119600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>77900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>106200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>129600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>109800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>95600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>117400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>165500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>91500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>63000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>118000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>101500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>99800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>95000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>121700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>110400</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E42" s="3">
         <v>2700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>7100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5900</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3907,216 +3997,225 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>631600</v>
+      </c>
+      <c r="E43" s="3">
         <v>713300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>614300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>746100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>712500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>692400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>619200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>705300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>422700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>454600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>370300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>447200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>467100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>481800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>373500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>449200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>456100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>491700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>372300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>416500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>451300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>581300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>502700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>582100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>547200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>571200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>520600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>826900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>863500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>849200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>841300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>884800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>810200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>822700</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>889300</v>
+      </c>
+      <c r="E44" s="3">
         <v>823700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>849500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>782900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>902700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>858000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>912700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>795100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>939100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>877400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>874800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>785600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>868700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>830100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>770400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>736800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>838000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>761900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>700500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>812200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>866300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>787400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>809600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>761000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>845800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>792500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>845500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>779800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>882000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>796400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>777400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>711900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>827100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>795500</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4141,502 +4240,517 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>335600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>353200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>311300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>304200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>289500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>333300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>330700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>286700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>273100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>263100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>267700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>236100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>268900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>189200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>160600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>165600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>169200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>176000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>184000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>103000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>116300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>96600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>97700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>111900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>112300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>104300</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1837600</v>
+      </c>
+      <c r="E46" s="3">
         <v>1842000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1762100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1778800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1832600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1790700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1772100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1783100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1844700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1825500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1706000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1679000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1790400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1799400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1611500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1615900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1723200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1656300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1460100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1542800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1692700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1687400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1582700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1604400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1679700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1705300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1641500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1772700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1979800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1843600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1816100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1803600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1871200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1832800</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>93800</v>
+      </c>
+      <c r="E47" s="3">
         <v>91900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>184200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>187500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>180800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>190500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>188500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>183200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>290100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>272000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>275700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>278000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>291900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>314300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>332000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>224000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>199400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>193800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>241600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>214900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>172200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>95900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>102200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>113100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>96900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>86500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>91000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>135200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>121700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>111200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>88400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>101500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>107500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>97100</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>349400</v>
+      </c>
+      <c r="E48" s="3">
         <v>350200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>350600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>351400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>334500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>320500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>320600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>305200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>288600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>282000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>290100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>283900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>286200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>287500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>294700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>296700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>304500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>379600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>377600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>382700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>390000</v>
-      </c>
-      <c r="X48" s="3">
-        <v>391200</v>
       </c>
       <c r="Y48" s="3">
         <v>391200</v>
       </c>
       <c r="Z48" s="3">
+        <v>391200</v>
+      </c>
+      <c r="AA48" s="3">
         <v>305800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>290300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>289600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>289700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>290600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>287400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>286700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>294800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>298500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>300400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>303300</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>330100</v>
+      </c>
+      <c r="E49" s="3">
         <v>341200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>340200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>349600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>359600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>368400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>379200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>388300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>397800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>372800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>383400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>393200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>403600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>413600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>425400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>419600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>428200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>435700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>444200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>452200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1140300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1148800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1156500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1167400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1174500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1182500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1193100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1205400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1216400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1220900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1230700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1239000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1247500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1292400</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4853,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4960,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>221600</v>
+      </c>
+      <c r="E52" s="3">
         <v>220200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>237700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>229500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>232500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>219600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>223300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>219200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>120800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>128100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>103100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>107500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>91300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>87900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>87300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>195400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>195700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>123600</v>
-      </c>
-      <c r="U52" s="3">
-        <v>122700</v>
       </c>
       <c r="V52" s="3">
         <v>122700</v>
       </c>
       <c r="W52" s="3">
+        <v>122700</v>
+      </c>
+      <c r="X52" s="3">
         <v>118300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>112100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>117000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>78700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>79200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>80300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>72500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>67800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>69100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>66100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>65200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>65400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>67500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>64700</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5174,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2832600</v>
+      </c>
+      <c r="E54" s="3">
         <v>2845600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2874800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2896700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2939900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2889700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2883600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2879100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2942000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2880500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2758400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2741600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2863500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2902700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2750800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2751500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2851000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2789000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2646200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2715400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3513600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3435500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3349600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3269300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3320500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3344300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3287800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3471700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3674400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3528500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3495200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3507900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>3594100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>3590400</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5322,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,632 +5361,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>644900</v>
+      </c>
+      <c r="E57" s="3">
         <v>731300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>657000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>745400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>683300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>688700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>717400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>725000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>702500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>714700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>655600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>681300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>715500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>773200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>593100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>609300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>677100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>690800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>549700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>862100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>802600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>766500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>625400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>648400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>688100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>662700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>588000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>610400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>654800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>634600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>536000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>616900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>547700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>545400</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>456300</v>
+      </c>
+      <c r="E58" s="3">
         <v>393700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>478100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>341800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>366600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>236400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>142100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>109700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>211000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>177000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>145000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>29000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>135000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>143800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>142800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>153800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>208800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>111000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>136000</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>95000</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
       <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
         <v>25800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>24000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>51100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>80300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>110400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>92600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>253800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>106800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>177800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>73800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>212800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>183600</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E59" s="3">
         <v>36300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>35500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>37400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>40300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>40100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>37500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>36900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>260300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>252100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>242900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>305300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>281600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>276100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>332000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>326700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>315100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>271100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>293100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>212800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>303800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>294900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>223000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>203300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>193400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>225900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>218800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>205400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>191500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>209300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>188300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>213300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>228000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>217700</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1305400</v>
+      </c>
+      <c r="E60" s="3">
         <v>1344400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1357500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1332600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1283700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1148500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1087700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1085300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1173700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1143800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1043600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1015700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1132100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1193100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1067900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1089700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1200900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1072900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>978800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1074900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1201500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1061400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>874200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>875700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>932700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>968900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>917300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>908400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1100100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>950600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>902100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>903900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>988500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>946700</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>423500</v>
+      </c>
+      <c r="E61" s="3">
         <v>424500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>434800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>434600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>538900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>541200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>538400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>531600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>451900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>485500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>488800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>488600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>488400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>488100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>487800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>487500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>487900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>588300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>588000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>587800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>587500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>663500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>718100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>725300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>732600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>738300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>743700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>922000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>931400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>991200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>998500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>998300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1001800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1010200</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>113800</v>
+      </c>
+      <c r="E62" s="3">
         <v>113200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>130000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>23400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>145100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>144900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>146200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>24500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>214000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>209000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>199000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>194800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>198900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>209600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>214500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>209600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>227600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>235100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>224700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>216200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>252700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>251900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>253900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>187700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>182500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>181300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>179600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>179500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>179900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>219700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>210200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>211300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>217800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>227400</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6108,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6215,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6322,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1842700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1882200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1922300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1895000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1967800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1834600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1772400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1760600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1840700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1839600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1732500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1700000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1820300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1891600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1771500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1788300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1918100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1898200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1793600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1881200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2044100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1979600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1849300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1792000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1851400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1892300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1844600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2009900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2211400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2161500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2110700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2113500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2208000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2184300</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6470,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6575,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6682,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6789,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6896,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>806800</v>
+      </c>
+      <c r="E72" s="3">
         <v>775500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>772000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>831500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>802900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>902800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>948700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>972100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>962900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>934600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>905600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>921700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>918300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>886900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>864200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>855700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>852200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>828700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>799600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>799700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1433200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1434800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1492800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1483500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1480100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1473400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1469000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1497800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1501000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1429700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1450200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1481200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1482600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1517800</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7110,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7217,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7324,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>989600</v>
+      </c>
+      <c r="E76" s="3">
         <v>963000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>952000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1001100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>971500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1054300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1110300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1117500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1101300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1040900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1025900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1041700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1043200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1011100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>979300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>963200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>932900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>890800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>852600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>834100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1469400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1455800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1500400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1477300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1469100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1452000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1443100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1461800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1463000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1366900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1384500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1394400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1386100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1406100</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7538,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45682</v>
+      </c>
+      <c r="E80" s="2">
         <v>45591</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45500</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45409</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45318</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45227</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45136</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45045</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44954</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44863</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44772</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44590</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44499</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44408</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44310</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44219</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44128</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44037</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43946</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43855</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43764</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43673</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43582</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43491</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43400</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43309</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43218</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43127</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43036</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42945</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42854</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42763</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>31300</v>
+      </c>
+      <c r="E81" s="3">
         <v>26800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>13700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>67000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>47700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>40000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>31200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>75000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>53900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>54100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>24600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>63900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>57000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>48300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>34000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>28800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>48800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>54100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>24400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-608600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>23200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-33100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>30000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>28000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>31200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>28900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>20900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>109000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>40200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>30800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>61700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>24500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>45800</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,49 +7798,50 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E83" s="3">
         <v>12200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>11400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>11600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>11700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>11600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>10800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>11200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>21200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>20900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>20200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>20600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>20400</v>
-      </c>
-      <c r="P83" s="3">
-        <v>20500</v>
       </c>
       <c r="Q83" s="3">
         <v>20500</v>
@@ -7651,19 +7850,19 @@
         <v>20500</v>
       </c>
       <c r="S83" s="3">
+        <v>20500</v>
+      </c>
+      <c r="T83" s="3">
         <v>19500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>19000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>19900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>20300</v>
-      </c>
-      <c r="W83" s="3">
-        <v>20600</v>
       </c>
       <c r="X83" s="3">
         <v>20600</v>
@@ -7672,40 +7871,43 @@
         <v>20600</v>
       </c>
       <c r="Z83" s="3">
+        <v>20600</v>
+      </c>
+      <c r="AA83" s="3">
         <v>20300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>20500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>21100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>20900</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>21000</v>
       </c>
       <c r="AE83" s="3">
         <v>21000</v>
       </c>
       <c r="AF83" s="3">
+        <v>21000</v>
+      </c>
+      <c r="AG83" s="3">
         <v>20700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>21100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>20800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>21000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8010,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8117,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8224,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8331,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8438,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-276400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-173700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-285000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-69500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-234600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-231900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-253400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-26700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-208000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-217600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-302500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-146900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-295100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-225600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-313400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-125600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-181900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-193200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-229800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-74600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-154300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>30600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-45200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-28200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-123900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>205500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>138900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-37100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>123100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-46000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>175400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>42700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>17500</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8586,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-12700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-16400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-17700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-16400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-17100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-21800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-15700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-14600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-6700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-6400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-8900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-10000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-14000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-8900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-26800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-11800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-11900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-10200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-15000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-11800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-9800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-6700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-9600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-8100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-14300</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8798,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8905,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>209800</v>
+      </c>
+      <c r="E94" s="3">
         <v>291000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>258300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>241500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>263100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>231100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>223800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>234300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>219400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>209500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>238400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>292600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>338800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>262600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>345000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>194800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>221000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>261500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>133400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>172700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>137000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>92700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>96800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>63200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>131200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>138800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>7600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>14300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>5500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>2800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9053,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8829,43 +9063,43 @@
         <v>22900</v>
       </c>
       <c r="E96" s="3">
-        <v>23300</v>
+        <v>22900</v>
       </c>
       <c r="F96" s="3">
         <v>23300</v>
       </c>
       <c r="G96" s="3">
+        <v>23300</v>
+      </c>
+      <c r="H96" s="3">
         <v>24700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>24900</v>
-      </c>
-      <c r="I96" s="3">
-        <v>25400</v>
       </c>
       <c r="J96" s="3">
         <v>25400</v>
       </c>
       <c r="K96" s="3">
+        <v>25400</v>
+      </c>
+      <c r="L96" s="3">
         <v>-25200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-25300</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-25400</v>
       </c>
       <c r="N96" s="3">
         <v>-25400</v>
       </c>
       <c r="O96" s="3">
-        <v>-25300</v>
+        <v>-25400</v>
       </c>
       <c r="P96" s="3">
         <v>-25300</v>
       </c>
       <c r="Q96" s="3">
-        <v>-25100</v>
+        <v>-25300</v>
       </c>
       <c r="R96" s="3">
         <v>-25100</v>
@@ -8874,58 +9108,61 @@
         <v>-25100</v>
       </c>
       <c r="T96" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="U96" s="3">
         <v>-25000</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-24900</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-25000</v>
       </c>
       <c r="X96" s="3">
         <v>-25000</v>
       </c>
       <c r="Y96" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-25500</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-24700</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-24800</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-24700</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-25300</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-24600</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-24700</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-24800</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-25200</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-25000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-23300</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-23500</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9265,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9372,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9479,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-107700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>58800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-181800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-20900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>9900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-23100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-194400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-9600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>4100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>73400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-162800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-32000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-20400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-38000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-82700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-26600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-48700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>135300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-123200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-6300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-105500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-36200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-55700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-56800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-58900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-183800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-188200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>50100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-135200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>43200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-206200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-34000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-3800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>5200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-6000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>5200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-6000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>4000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>2700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-3100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>2100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>3900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>2100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>1300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-22900</v>
+      </c>
+      <c r="E102" s="3">
         <v>9900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>33600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-9500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>10100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-51100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>12400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>7500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-23000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>10900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>17200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-12700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>16500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>19900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>41600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-28200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-23400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>19800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>14100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-21800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-48100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>74000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>28500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-55000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>16500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>4800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-26800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>11400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>20400</v>
       </c>
     </row>
